--- a/공지사항.xlsx
+++ b/공지사항.xlsx
@@ -20,7 +20,79 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="34">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="32">
+  <x:si>
+    <x:t>봉사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종료일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시작일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주의</x:t>
+  </x:si>
+  <x:si>
+    <x:t>중요</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>제목</x:t>
+  </x:si>
+  <x:si>
+    <x:t>항목</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Y</x:t>
+  </x:si>
+  <x:si>
+    <x:t>행사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구세군사관대학원대학교에서 진행</x:t>
+  </x:si>
+  <x:si>
+    <x:t>남서울지방 여름성회(8/12~14)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>열 이름과 순서를 변경하지 마세요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수원역 무료급식(7월14일)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영문출발은 오전10시 30분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Y=중요공지, N=일반공지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시작일·종료일 사이에만 앱에 표시됩니다. 중요=Y인 공지는 상단에 강조됩니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공지 노출 시작일. yyyy-mm-dd 형식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소그룹 모임을 매월 첫째주와 셋째주로 변경 합니다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장소 : 과천영문 (세부일정 추후 공지예정)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바자회 물품 후원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>짧고 분명하게 작성</x:t>
+  </x:si>
   <x:si>
     <x:t>소그룹 모임 변경안내</x:t>
   </x:si>
@@ -28,10 +100,13 @@
     <x:t>공지사항 표준양식</x:t>
   </x:si>
   <x:si>
-    <x:t>짧고 분명하게 작성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>바자회 물품 후원</x:t>
+    <x:t>가정단에서 바자회 물품 후원을 받습니다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공지 노출 종료일. 해당 날짜까지 표시</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일정·장소·준비사항 등을 자세히 작성</x:t>
   </x:si>
   <x:si>
     <x:t>공지/안내/행사/예배/교육/전도/봉사/회의/기타 중 선택</x:t>
@@ -40,88 +115,7 @@
     <x:t>salvation land 어린이 캠프(7월25일)</x:t>
   </x:si>
   <x:si>
-    <x:t>구세군사관대학원대학교에서 진행</x:t>
-  </x:si>
-  <x:si>
-    <x:t>열 이름과 순서를 변경하지 마세요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>남서울지방 여름성회(8/12~14)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수원역 생수나눔 봉사(8월1일)</x:t>
-  </x:si>
-  <x:si>
     <x:t>작성 방법</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가정단에서 바자회 물품 후원을 받습니다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공지 노출 종료일. 해당 날짜까지 표시</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일정·장소·준비사항 등을 자세히 작성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Y</x:t>
-  </x:si>
-  <x:si>
-    <x:t>항목</x:t>
-  </x:si>
-  <x:si>
-    <x:t>중요</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시작일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주의</x:t>
-  </x:si>
-  <x:si>
-    <x:t>봉사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>제목</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종료일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>행사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장소 : 과천영문 (세부일정 추후 공지예정)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소그룹 모임을 매월 첫째주와 셋째주로 변경 합니다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공지 노출 시작일. yyyy-mm-dd 형식</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시작일·종료일 사이에만 앱에 표시됩니다. 중요=Y인 공지는 상단에 강조됩니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영문출발 오전10시30분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Y=중요공지, N=일반공지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영문출발은 오전10시 30분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수원역 무료급식(7월14일)</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -174,28 +168,12 @@
       <x:color rgb="ffffffff"/>
       <x:b val="1"/>
     </x:font>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="Carlito"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff6b3442"/>
-          <x:i val="1"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="Carlito"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff6b3442"/>
-          <x:i val="1"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
+    <x:font>
+      <x:name val="Carlito"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff6b3442"/>
+      <x:i val="1"/>
+    </x:font>
   </x:fonts>
   <x:fills count="6">
     <x:fill>
@@ -789,6 +767,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ff8e1b33"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -990,7 +969,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:F199"/>
+  <x:dimension ref="A1:F198"/>
   <x:sheetFormatPr defaultColWidth="8.72265625" defaultRowHeight="13.550000000000001"/>
   <x:cols>
     <x:col min="1" max="1" width="16.453125" style="1" customWidth="1"/>
@@ -1003,7 +982,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:6" ht="32" customHeight="1">
       <x:c r="A1" s="30" t="s">
-        <x:v>1</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B1" s="30"/>
       <x:c r="C1" s="30"/>
@@ -1013,7 +992,7 @@
     </x:row>
     <x:row r="2" spans="1:6" ht="28" customHeight="1">
       <x:c r="A2" s="31" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B2" s="31"/>
       <x:c r="C2" s="31"/>
@@ -1023,22 +1002,22 @@
     </x:row>
     <x:row r="4" spans="1:6" ht="24" customHeight="1">
       <x:c r="A4" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>22</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D4" s="3" t="s">
-        <x:v>21</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E4" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F4" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:6">
@@ -1049,16 +1028,16 @@
         <x:v>46217</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>19</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D5" s="5" t="s">
-        <x:v>33</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E5" s="15" t="s">
-        <x:v>32</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F5" s="6" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6">
@@ -1069,16 +1048,16 @@
         <x:v>46234</x:v>
       </x:c>
       <x:c r="C6" s="9" t="s">
-        <x:v>25</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D6" s="9" t="s">
-        <x:v>3</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E6" s="16" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F6" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:6">
@@ -1089,36 +1068,36 @@
         <x:v>46222</x:v>
       </x:c>
       <x:c r="C7" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D7" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E7" s="15" t="s">
-        <x:v>27</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F7" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6">
       <x:c r="A8" s="29">
         <x:v>46221</x:v>
       </x:c>
-      <x:c r="B8" s="19">
-        <x:v>46236</x:v>
+      <x:c r="B8" s="18">
+        <x:v>46228</x:v>
       </x:c>
       <x:c r="C8" s="20" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D8" s="20" t="s">
-        <x:v>9</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E8" s="21" t="s">
-        <x:v>30</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F8" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:6">
@@ -1126,40 +1105,28 @@
         <x:v>46221</x:v>
       </x:c>
       <x:c r="B9" s="18">
-        <x:v>46228</x:v>
+        <x:v>46249</x:v>
       </x:c>
       <x:c r="C9" s="20" t="s">
-        <x:v>25</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D9" s="20" t="s">
-        <x:v>5</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E9" s="21" t="s">
-        <x:v>6</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F9" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:6">
-      <x:c r="A10" s="29">
-        <x:v>46221</x:v>
-      </x:c>
-      <x:c r="B10" s="18">
-        <x:v>46249</x:v>
-      </x:c>
-      <x:c r="C10" s="20" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D10" s="20" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E10" s="21" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="F10" s="5" t="s">
-        <x:v>14</x:v>
-      </x:c>
+      <x:c r="A10" s="18"/>
+      <x:c r="B10" s="19"/>
+      <x:c r="C10" s="20"/>
+      <x:c r="D10" s="20"/>
+      <x:c r="E10" s="21"/>
+      <x:c r="F10" s="22"/>
     </x:row>
     <x:row r="11" spans="1:6">
       <x:c r="A11" s="18"/>
@@ -1306,12 +1273,12 @@
       <x:c r="F28" s="22"/>
     </x:row>
     <x:row r="29" spans="1:6">
-      <x:c r="A29" s="18"/>
-      <x:c r="B29" s="19"/>
-      <x:c r="C29" s="20"/>
-      <x:c r="D29" s="20"/>
-      <x:c r="E29" s="21"/>
-      <x:c r="F29" s="22"/>
+      <x:c r="A29" s="7"/>
+      <x:c r="B29" s="8"/>
+      <x:c r="C29" s="9"/>
+      <x:c r="D29" s="9"/>
+      <x:c r="E29" s="16"/>
+      <x:c r="F29" s="10"/>
     </x:row>
     <x:row r="30" spans="1:6">
       <x:c r="A30" s="7"/>
@@ -2658,44 +2625,31 @@
       <x:c r="F197" s="10"/>
     </x:row>
     <x:row r="198" spans="1:6">
-      <x:c r="A198" s="7"/>
-      <x:c r="B198" s="8"/>
-      <x:c r="C198" s="9"/>
-      <x:c r="D198" s="9"/>
-      <x:c r="E198" s="16"/>
-      <x:c r="F198" s="10"/>
-    </x:row>
-    <x:row r="199" spans="1:6">
-      <x:c r="A199" s="11"/>
-      <x:c r="B199" s="12"/>
-      <x:c r="C199" s="13"/>
-      <x:c r="D199" s="13"/>
-      <x:c r="E199" s="17"/>
-      <x:c r="F199" s="14"/>
+      <x:c r="A198" s="11"/>
+      <x:c r="B198" s="12"/>
+      <x:c r="C198" s="13"/>
+      <x:c r="D198" s="13"/>
+      <x:c r="E198" s="17"/>
+      <x:c r="F198" s="14"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells count="2">
     <x:mergeCell ref="A1:F1"/>
     <x:mergeCell ref="A2:F2"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="A5:F5 A6:E10 A11:F199">
+  <x:conditionalFormatting sqref="A5:F5 A6:E9 A10:F198">
     <x:cfRule type="expression" dxfId="12" priority="6">
       <x:formula>$F5="Y"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="F8:F8">
-    <x:cfRule type="expression" dxfId="12" priority="5">
+    <x:cfRule type="expression" dxfId="12" priority="4">
       <x:formula>$F8="Y"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="F9:F9">
-    <x:cfRule type="expression" dxfId="12" priority="4">
+    <x:cfRule type="expression" dxfId="12" priority="3">
       <x:formula>$F9="Y"</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="F10:F10">
-    <x:cfRule type="expression" dxfId="12" priority="3">
-      <x:formula>$F10="Y"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="F6:F6">
@@ -2709,10 +2663,10 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="2">
-    <x:dataValidation type="list" sqref="C5:C199">
+    <x:dataValidation type="list" sqref="C5:C198">
       <x:formula1>"공지,안내,행사,예배,교육,전도,봉사,회의,기타"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="F5:F199">
+    <x:dataValidation type="list" sqref="F5:F198">
       <x:formula1>"Y,N"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
@@ -2733,66 +2687,66 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="23" t="s">
-        <x:v>15</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B1" s="24" t="s">
-        <x:v>10</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="25" t="s">
-        <x:v>17</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B2" s="27" t="s">
-        <x:v>28</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="25" t="s">
-        <x:v>22</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="27" t="s">
-        <x:v>12</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="25" t="s">
-        <x:v>24</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B4" s="27" t="s">
-        <x:v>4</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="25" t="s">
-        <x:v>21</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B5" s="27" t="s">
-        <x:v>2</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="25" t="s">
-        <x:v>20</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B6" s="27" t="s">
-        <x:v>13</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="25" t="s">
-        <x:v>16</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B7" s="27" t="s">
-        <x:v>31</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="26" t="s">
-        <x:v>18</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="28" t="s">
-        <x:v>7</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/공지사항.xlsx
+++ b/공지사항.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="25340" windowHeight="11490" tabRatio="500"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="4294939900" windowHeight="17090" tabRatio="500"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="공지사항" sheetId="1" r:id="rId4"/>
@@ -20,18 +20,105 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="40">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="42">
+  <x:si>
+    <x:t>공지 노출 시작일. yyyy-mm-dd 형식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장소 : 과천영문 (세부일정 추후 공지예정)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소그룹 모임을 매월 첫째주와 셋째주로 변경 합니다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장소 :  구세군사관대학원대학교, 8/15일(토)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>열 이름과 순서를 변경하지 마세요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구세군사관대학원대학교에서 진행</x:t>
+  </x:si>
   <x:si>
     <x:t>장소 : 과천영문, 8/13일</x:t>
   </x:si>
   <x:si>
+    <x:t>남서울지방 여름성회(8/12~14)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영문출발은 오전10시 30분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Y=중요공지, N=일반공지</x:t>
+  </x:si>
+  <x:si>
     <x:t>수원역 무료급식(7월14일)</x:t>
   </x:si>
   <x:si>
-    <x:t>Y=중요공지, N=일반공지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영문출발은 오전10시 30분</x:t>
+    <x:t>일정·장소·준비사항 등을 자세히 작성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가정단에서 바자회 물품 후원을 받습니다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공지 노출 종료일. 해당 날짜까지 표시</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">담임사관님, 목양담당사관님 여름휴가 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>휴가기간 : 8/3(월)~8/8(토)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>작성 방법</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여성캠프 안내</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소그룹 모임 변경안내</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공지사항 표준양식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>짧고 분명하게 작성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영문 악대캠프 시행</x:t>
+  </x:si>
+  <x:si>
+    <x:t>박옥영사관님 추도예배</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바자회 물품 후원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공지/안내/행사/예배/교육/전도/봉사/회의/기타 중 선택</x:t>
+  </x:si>
+  <x:si>
+    <x:t>salvation land 어린이 캠프(7월25일)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장소 : 세종하늘공원, 8/8(토), 오전9시 영문출발</x:t>
+  </x:si>
+  <x:si>
+    <x:t>행사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시작일·종료일 사이에만 앱에 표시됩니다. 중요=Y인 공지는 상단에 강조됩니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여름 수련회 비용마련을 위한 매식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>청년부 점심식사 매식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시작일</x:t>
   </x:si>
   <x:si>
     <x:t>제목</x:t>
@@ -43,103 +130,22 @@
     <x:t>종료일</x:t>
   </x:si>
   <x:si>
-    <x:t>시작일</x:t>
+    <x:t>공지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>항목</x:t>
+  </x:si>
+  <x:si>
+    <x:t>중요</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주의</x:t>
   </x:si>
   <x:si>
     <x:t>봉사</x:t>
   </x:si>
   <x:si>
     <x:t>내용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>중요</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공지 노출 종료일. 해당 날짜까지 표시</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일정·장소·준비사항 등을 자세히 작성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가정단에서 바자회 물품 후원을 받습니다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>남서울지방 여름성회(8/12~14)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구세군사관대학원대학교에서 진행</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공지사항 표준양식</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소그룹 모임 변경안내</x:t>
-  </x:si>
-  <x:si>
-    <x:t>바자회 물품 후원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>짧고 분명하게 작성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>항목</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주의</x:t>
-  </x:si>
-  <x:si>
-    <x:t>행사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>열 이름과 순서를 변경하지 마세요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>작성 방법</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시작일·종료일 사이에만 앱에 표시됩니다. 중요=Y인 공지는 상단에 강조됩니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장소 : 세종하늘공원, 8/8(토), 오전9시 영문출발</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영문 악대캠프 시행</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">담임사관님, 목양담당사관님 여름휴가 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>장소 : 과천영문 (세부일정 추후 공지예정)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소그룹 모임을 매월 첫째주와 셋째주로 변경 합니다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장소 :  구세군사관대학원대학교, 8/15일(토)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>휴가기간 : 8/3(월)~8/8(토)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>박옥영사관님 추도예배</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공지/안내/행사/예배/교육/전도/봉사/회의/기타 중 선택</x:t>
-  </x:si>
-  <x:si>
-    <x:t>salvation land 어린이 캠프(7월25일)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공지 노출 시작일. yyyy-mm-dd 형식</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여성캠프 안내</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -150,54 +156,192 @@
     <x:numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </x:numFmts>
   <x:fonts count="9">
-    <x:font>
-      <x:name val="Carlito"/>
-      <x:sz val="11"/>
-      <x:color rgb="ff000000"/>
-    </x:font>
-    <x:font>
-      <x:name val="Carlito"/>
-      <x:sz val="11"/>
-      <x:color rgb="ff000000"/>
-    </x:font>
-    <x:font>
-      <x:name val="Carlito"/>
-      <x:sz val="11"/>
-      <x:color rgb="ff000000"/>
-    </x:font>
-    <x:font>
-      <x:name val="Carlito"/>
-      <x:sz val="11"/>
-      <x:color rgb="ff000000"/>
-    </x:font>
-    <x:font>
-      <x:name val="Carlito"/>
-      <x:sz val="11"/>
-      <x:color rgb="ff000000"/>
-    </x:font>
-    <x:font>
-      <x:name val="Carlito"/>
-      <x:sz val="11"/>
-      <x:color rgb="ff000000"/>
-    </x:font>
-    <x:font>
-      <x:name val="Carlito"/>
-      <x:sz val="11"/>
-      <x:color rgb="ffffffff"/>
-      <x:b val="1"/>
-    </x:font>
-    <x:font>
-      <x:name val="Carlito"/>
-      <x:sz val="16"/>
-      <x:color rgb="ffffffff"/>
-      <x:b val="1"/>
-    </x:font>
-    <x:font>
-      <x:name val="Carlito"/>
-      <x:sz val="11"/>
-      <x:color rgb="ff6b3442"/>
-      <x:i val="1"/>
-    </x:font>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="Carlito"/>
+          <x:sz val="11"/>
+          <x:color rgb="ff000000"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="Carlito"/>
+          <x:sz val="11"/>
+          <x:color rgb="ff000000"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="Carlito"/>
+          <x:sz val="11"/>
+          <x:color rgb="ff000000"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="Carlito"/>
+          <x:sz val="11"/>
+          <x:color rgb="ff000000"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="Carlito"/>
+          <x:sz val="11"/>
+          <x:color rgb="ff000000"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="Carlito"/>
+          <x:sz val="11"/>
+          <x:color rgb="ff000000"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="Carlito"/>
+          <x:sz val="11"/>
+          <x:color rgb="ff000000"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="Carlito"/>
+          <x:sz val="11"/>
+          <x:color rgb="ff000000"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="Carlito"/>
+          <x:sz val="11"/>
+          <x:color rgb="ff000000"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="Carlito"/>
+          <x:sz val="11"/>
+          <x:color rgb="ff000000"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="Carlito"/>
+          <x:sz val="11"/>
+          <x:color rgb="ff000000"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="Carlito"/>
+          <x:sz val="11"/>
+          <x:color rgb="ff000000"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="Carlito"/>
+          <x:sz val="11"/>
+          <x:color rgb="ffffffff"/>
+          <x:b val="1"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="Carlito"/>
+          <x:sz val="11"/>
+          <x:color rgb="ffffffff"/>
+          <x:b val="1"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="Carlito"/>
+          <x:sz val="16"/>
+          <x:color rgb="ffffffff"/>
+          <x:b val="1"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="Carlito"/>
+          <x:sz val="16"/>
+          <x:color rgb="ffffffff"/>
+          <x:b val="1"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="Carlito"/>
+          <x:sz val="11"/>
+          <x:color rgb="ff6b3442"/>
+          <x:i val="1"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="Carlito"/>
+          <x:sz val="11"/>
+          <x:color rgb="ff6b3442"/>
+          <x:i val="1"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
   </x:fonts>
   <x:fills count="6">
     <x:fill>
@@ -395,6 +539,19 @@
     </x:xf>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
         <x:xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
           <x:alignment horizontal="center" vertical="center"/>
           <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
@@ -409,19 +566,6 @@
     <x:xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center" wrapText="1"/>
     </x:xf>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
   </x:cellXfs>
   <x:cellStyles count="2">
     <x:cellStyle name="표준" xfId="0" builtinId="0" iLevel="0"/>
@@ -801,6 +945,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ff8e1b33"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1014,43 +1159,43 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:6" ht="32" customHeight="1">
-      <x:c r="A1" s="29" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B1" s="29"/>
-      <x:c r="C1" s="29"/>
-      <x:c r="D1" s="29"/>
-      <x:c r="E1" s="29"/>
-      <x:c r="F1" s="29"/>
+      <x:c r="A1" s="30" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B1" s="30"/>
+      <x:c r="C1" s="30"/>
+      <x:c r="D1" s="30"/>
+      <x:c r="E1" s="30"/>
+      <x:c r="F1" s="30"/>
     </x:row>
     <x:row r="2" spans="1:6" ht="28" customHeight="1">
-      <x:c r="A2" s="30" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B2" s="30"/>
-      <x:c r="C2" s="30"/>
-      <x:c r="D2" s="30"/>
-      <x:c r="E2" s="30"/>
-      <x:c r="F2" s="30"/>
+      <x:c r="A2" s="31" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B2" s="31"/>
+      <x:c r="C2" s="31"/>
+      <x:c r="D2" s="31"/>
+      <x:c r="E2" s="31"/>
+      <x:c r="F2" s="31"/>
     </x:row>
     <x:row r="4" spans="1:6" ht="24" customHeight="1">
       <x:c r="A4" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D4" s="3" t="s">
-        <x:v>4</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E4" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F4" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:6">
@@ -1061,16 +1206,16 @@
         <x:v>46217</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D5" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E5" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D5" s="5" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E5" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F5" s="31" t="s">
-        <x:v>5</x:v>
+      <x:c r="F5" s="29" t="s">
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6">
@@ -1081,16 +1226,16 @@
         <x:v>46234</x:v>
       </x:c>
       <x:c r="C6" s="8" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D6" s="8" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E6" s="15" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F6" s="31" t="s">
-        <x:v>5</x:v>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F6" s="29" t="s">
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:6">
@@ -1101,16 +1246,16 @@
         <x:v>46222</x:v>
       </x:c>
       <x:c r="C7" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D7" s="5" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="E7" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F7" s="31" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F7" s="29" t="s">
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6">
@@ -1121,16 +1266,16 @@
         <x:v>46228</x:v>
       </x:c>
       <x:c r="C8" s="19" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D8" s="19" t="s">
-        <x:v>37</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E8" s="20" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F8" s="31" t="s">
         <x:v>5</x:v>
+      </x:c>
+      <x:c r="F8" s="29" t="s">
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:6">
@@ -1141,16 +1286,16 @@
         <x:v>46249</x:v>
       </x:c>
       <x:c r="C9" s="19" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D9" s="19" t="s">
-        <x:v>15</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E9" s="20" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F9" s="31" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F9" s="29" t="s">
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:6">
@@ -1161,16 +1306,16 @@
         <x:v>46242</x:v>
       </x:c>
       <x:c r="C10" s="19" t="s">
-        <x:v>11</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D10" s="19" t="s">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E10" s="20" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F10" s="29" t="s">
         <x:v>34</x:v>
-      </x:c>
-      <x:c r="F10" s="31" t="s">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:6">
@@ -1178,19 +1323,19 @@
         <x:v>46237</x:v>
       </x:c>
       <x:c r="B11" s="17">
-        <x:v>46242</x:v>
+        <x:v>46249</x:v>
       </x:c>
       <x:c r="C11" s="19" t="s">
-        <x:v>11</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D11" s="19" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E11" s="20" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="F11" s="31" t="s">
-        <x:v>5</x:v>
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F11" s="29" t="s">
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:6">
@@ -1198,19 +1343,19 @@
         <x:v>46237</x:v>
       </x:c>
       <x:c r="B12" s="17">
-        <x:v>46242</x:v>
+        <x:v>46249</x:v>
       </x:c>
       <x:c r="C12" s="19" t="s">
-        <x:v>11</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D12" s="19" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E12" s="20" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F12" s="31" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F12" s="29" t="s">
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:6">
@@ -1218,28 +1363,40 @@
         <x:v>46237</x:v>
       </x:c>
       <x:c r="B13" s="17">
-        <x:v>46242</x:v>
+        <x:v>46249</x:v>
       </x:c>
       <x:c r="C13" s="19" t="s">
-        <x:v>11</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D13" s="19" t="s">
-        <x:v>29</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E13" s="20" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="F13" s="31" t="s">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F13" s="29" t="s">
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:6">
-      <x:c r="A14" s="17"/>
-      <x:c r="B14" s="18"/>
-      <x:c r="C14" s="19"/>
-      <x:c r="D14" s="19"/>
-      <x:c r="E14" s="20"/>
-      <x:c r="F14" s="21"/>
+      <x:c r="A14" s="28">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="B14" s="17">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="C14" s="19" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D14" s="19" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E14" s="20" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F14" s="29" t="s">
+        <x:v>34</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" spans="1:6">
       <x:c r="A15" s="17"/>
@@ -2718,44 +2875,59 @@
     <x:mergeCell ref="A1:F1"/>
     <x:mergeCell ref="A2:F2"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="A5:F10 D11:E12 D13:D13 A14:F198">
-    <x:cfRule type="expression" dxfId="12" priority="9">
+  <x:conditionalFormatting sqref="A5:F10 D11:E12 D13:D13 A15:F198">
+    <x:cfRule type="expression" dxfId="12" priority="12">
       <x:formula>$F5="Y"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="A11:C11">
-    <x:cfRule type="expression" dxfId="12" priority="8">
+  <x:conditionalFormatting sqref="A11:A11 C11:C11">
+    <x:cfRule type="expression" dxfId="12" priority="11">
       <x:formula>$F11="Y"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="F11:F11">
-    <x:cfRule type="expression" dxfId="12" priority="7">
+    <x:cfRule type="expression" dxfId="12" priority="10">
       <x:formula>$F11="Y"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="A12:C12">
-    <x:cfRule type="expression" dxfId="12" priority="6">
+  <x:conditionalFormatting sqref="A12:A12 C12:C12">
+    <x:cfRule type="expression" dxfId="12" priority="9">
       <x:formula>$F12="Y"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="F12:F12">
-    <x:cfRule type="expression" dxfId="12" priority="5">
+    <x:cfRule type="expression" dxfId="12" priority="8">
       <x:formula>$F12="Y"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="E13:E13">
+    <x:cfRule type="expression" dxfId="12" priority="7">
+      <x:formula>$F13="Y"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="F13:F13">
+    <x:cfRule type="expression" dxfId="12" priority="6">
+      <x:formula>$F13="Y"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="A13:C13">
     <x:cfRule type="expression" dxfId="12" priority="4">
       <x:formula>$F13="Y"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="F13:F13">
+  <x:conditionalFormatting sqref="B12:B12">
     <x:cfRule type="expression" dxfId="12" priority="3">
-      <x:formula>$F13="Y"</x:formula>
+      <x:formula>$F12="Y"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="A13:C13">
+  <x:conditionalFormatting sqref="B11:B11">
+    <x:cfRule type="expression" dxfId="12" priority="2">
+      <x:formula>$F11="Y"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="A14:F14">
     <x:cfRule type="expression" dxfId="12" priority="1">
-      <x:formula>$F13="Y"</x:formula>
+      <x:formula>$F14="Y"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="2">
@@ -2783,39 +2955,39 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="22" t="s">
-        <x:v>21</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B1" s="23" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="24" t="s">
-        <x:v>7</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B2" s="26" t="s">
-        <x:v>38</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="24" t="s">
-        <x:v>6</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B3" s="26" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="24" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B4" s="26" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="24" t="s">
-        <x:v>4</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B5" s="26" t="s">
         <x:v>20</x:v>
@@ -2823,26 +2995,26 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="24" t="s">
-        <x:v>9</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B6" s="26" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="24" t="s">
-        <x:v>10</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B7" s="26" t="s">
-        <x:v>2</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="25" t="s">
-        <x:v>23</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B8" s="27" t="s">
-        <x:v>25</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/공지사항.xlsx
+++ b/공지사항.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="4294939900" windowHeight="17090" tabRatio="500"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="25340" windowHeight="11490" tabRatio="500"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="공지사항" sheetId="1" r:id="rId4"/>
@@ -25,127 +25,127 @@
     <x:t>공지 노출 시작일. yyyy-mm-dd 형식</x:t>
   </x:si>
   <x:si>
+    <x:t>소그룹 모임을 매월 첫째주와 셋째주로 변경 합니다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장소 :  구세군사관대학원대학교, 8/15일(토)</x:t>
+  </x:si>
+  <x:si>
     <x:t>장소 : 과천영문 (세부일정 추후 공지예정)</x:t>
   </x:si>
   <x:si>
-    <x:t>소그룹 모임을 매월 첫째주와 셋째주로 변경 합니다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장소 :  구세군사관대학원대학교, 8/15일(토)</x:t>
+    <x:t>시작일·종료일 사이에만 앱에 표시됩니다. 중요=Y인 공지는 상단에 강조됩니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영문출발은 오전10시 30분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Y=중요공지, N=일반공지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수원역 무료급식(7월14일)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>청년부 점심식사 매식(8/16)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공지사항 표준양식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바자회 물품 후원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>짧고 분명하게 작성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영문 악대캠프 시행</x:t>
+  </x:si>
+  <x:si>
+    <x:t>박옥영사관님 추도예배</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소그룹 모임 변경안내</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공지/안내/행사/예배/교육/전도/봉사/회의/기타 중 선택</x:t>
+  </x:si>
+  <x:si>
+    <x:t>salvation land 어린이 캠프(7월25일)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장소 : 세종하늘공원, 8/8(토), 오전9시 영문출발</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여성캠프 안내</x:t>
+  </x:si>
+  <x:si>
+    <x:t>작성 방법</x:t>
+  </x:si>
+  <x:si>
+    <x:t>휴가기간 : 8/3(월)~8/8(토)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가정단에서 바자회 물품 후원을 받습니다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공지 노출 종료일. 해당 날짜까지 표시</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">담임사관님, 목양담당사관님 여름휴가 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>일정·장소·준비사항 등을 자세히 작성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종료일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>항목</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주의</x:t>
+  </x:si>
+  <x:si>
+    <x:t>중요</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Y</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시작일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>제목</x:t>
+  </x:si>
+  <x:si>
+    <x:t>행사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>봉사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장소 : 과천영문, 8/13일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>남서울지방 여름성회(8/12~14)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구세군사관대학원대학교에서 진행</x:t>
   </x:si>
   <x:si>
     <x:t>열 이름과 순서를 변경하지 마세요.</x:t>
   </x:si>
   <x:si>
-    <x:t>구세군사관대학원대학교에서 진행</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장소 : 과천영문, 8/13일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>남서울지방 여름성회(8/12~14)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영문출발은 오전10시 30분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Y=중요공지, N=일반공지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수원역 무료급식(7월14일)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일정·장소·준비사항 등을 자세히 작성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가정단에서 바자회 물품 후원을 받습니다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공지 노출 종료일. 해당 날짜까지 표시</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">담임사관님, 목양담당사관님 여름휴가 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>휴가기간 : 8/3(월)~8/8(토)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>작성 방법</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여성캠프 안내</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소그룹 모임 변경안내</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공지사항 표준양식</x:t>
-  </x:si>
-  <x:si>
-    <x:t>짧고 분명하게 작성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영문 악대캠프 시행</x:t>
-  </x:si>
-  <x:si>
-    <x:t>박옥영사관님 추도예배</x:t>
-  </x:si>
-  <x:si>
-    <x:t>바자회 물품 후원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공지/안내/행사/예배/교육/전도/봉사/회의/기타 중 선택</x:t>
-  </x:si>
-  <x:si>
-    <x:t>salvation land 어린이 캠프(7월25일)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장소 : 세종하늘공원, 8/8(토), 오전9시 영문출발</x:t>
-  </x:si>
-  <x:si>
-    <x:t>행사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시작일·종료일 사이에만 앱에 표시됩니다. 중요=Y인 공지는 상단에 강조됩니다.</x:t>
-  </x:si>
-  <x:si>
     <x:t>여름 수련회 비용마련을 위한 매식</x:t>
-  </x:si>
-  <x:si>
-    <x:t>청년부 점심식사 매식</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시작일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>제목</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Y</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종료일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>항목</x:t>
-  </x:si>
-  <x:si>
-    <x:t>중요</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주의</x:t>
-  </x:si>
-  <x:si>
-    <x:t>봉사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내용</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -156,192 +156,54 @@
     <x:numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </x:numFmts>
   <x:fonts count="9">
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="Carlito"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff000000"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="Carlito"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff000000"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="Carlito"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff000000"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="Carlito"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff000000"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="Carlito"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff000000"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="Carlito"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff000000"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="Carlito"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff000000"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="Carlito"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff000000"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="Carlito"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff000000"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="Carlito"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff000000"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="Carlito"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff000000"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="Carlito"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff000000"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="Carlito"/>
-          <x:sz val="11"/>
-          <x:color rgb="ffffffff"/>
-          <x:b val="1"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="Carlito"/>
-          <x:sz val="11"/>
-          <x:color rgb="ffffffff"/>
-          <x:b val="1"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="Carlito"/>
-          <x:sz val="16"/>
-          <x:color rgb="ffffffff"/>
-          <x:b val="1"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="Carlito"/>
-          <x:sz val="16"/>
-          <x:color rgb="ffffffff"/>
-          <x:b val="1"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="Carlito"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff6b3442"/>
-          <x:i val="1"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="Carlito"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff6b3442"/>
-          <x:i val="1"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
+    <x:font>
+      <x:name val="Carlito"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
+      <x:name val="Carlito"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
+      <x:name val="Carlito"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
+      <x:name val="Carlito"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
+      <x:name val="Carlito"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
+      <x:name val="Carlito"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
+      <x:name val="Carlito"/>
+      <x:sz val="11"/>
+      <x:color rgb="ffffffff"/>
+      <x:b val="1"/>
+    </x:font>
+    <x:font>
+      <x:name val="Carlito"/>
+      <x:sz val="16"/>
+      <x:color rgb="ffffffff"/>
+      <x:b val="1"/>
+    </x:font>
+    <x:font>
+      <x:name val="Carlito"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff6b3442"/>
+      <x:i val="1"/>
+    </x:font>
   </x:fonts>
   <x:fills count="6">
     <x:fill>
@@ -945,7 +807,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ff8e1b33"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1160,7 +1021,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:6" ht="32" customHeight="1">
       <x:c r="A1" s="30" t="s">
-        <x:v>19</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B1" s="30"/>
       <x:c r="C1" s="30"/>
@@ -1170,7 +1031,7 @@
     </x:row>
     <x:row r="2" spans="1:6" ht="28" customHeight="1">
       <x:c r="A2" s="31" t="s">
-        <x:v>29</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B2" s="31"/>
       <x:c r="C2" s="31"/>
@@ -1183,19 +1044,19 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D4" s="3" t="s">
         <x:v>33</x:v>
       </x:c>
       <x:c r="E4" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F4" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:6">
@@ -1206,16 +1067,16 @@
         <x:v>46217</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D5" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E5" s="14" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F5" s="29" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6">
@@ -1226,16 +1087,16 @@
         <x:v>46234</x:v>
       </x:c>
       <x:c r="C6" s="8" t="s">
-        <x:v>27</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D6" s="8" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E6" s="15" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F6" s="29" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:6">
@@ -1246,16 +1107,16 @@
         <x:v>46222</x:v>
       </x:c>
       <x:c r="C7" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D7" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E7" s="14" t="s">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F7" s="29" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6">
@@ -1266,16 +1127,16 @@
         <x:v>46228</x:v>
       </x:c>
       <x:c r="C8" s="19" t="s">
-        <x:v>27</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D8" s="19" t="s">
-        <x:v>25</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E8" s="20" t="s">
-        <x:v>5</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F8" s="29" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:6">
@@ -1286,16 +1147,16 @@
         <x:v>46249</x:v>
       </x:c>
       <x:c r="C9" s="19" t="s">
-        <x:v>27</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D9" s="19" t="s">
-        <x:v>7</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E9" s="20" t="s">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F9" s="29" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:6">
@@ -1306,16 +1167,16 @@
         <x:v>46242</x:v>
       </x:c>
       <x:c r="C10" s="19" t="s">
-        <x:v>36</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D10" s="19" t="s">
-        <x:v>14</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E10" s="20" t="s">
-        <x:v>15</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F10" s="29" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:6">
@@ -1326,16 +1187,16 @@
         <x:v>46249</x:v>
       </x:c>
       <x:c r="C11" s="19" t="s">
-        <x:v>36</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D11" s="19" t="s">
-        <x:v>22</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E11" s="20" t="s">
-        <x:v>26</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F11" s="29" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:6">
@@ -1346,16 +1207,16 @@
         <x:v>46249</x:v>
       </x:c>
       <x:c r="C12" s="19" t="s">
-        <x:v>36</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D12" s="19" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E12" s="20" t="s">
-        <x:v>6</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F12" s="29" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:6">
@@ -1366,16 +1227,16 @@
         <x:v>46249</x:v>
       </x:c>
       <x:c r="C13" s="19" t="s">
-        <x:v>36</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D13" s="19" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E13" s="20" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F13" s="29" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:6">
@@ -1386,16 +1247,16 @@
         <x:v>46251</x:v>
       </x:c>
       <x:c r="C14" s="19" t="s">
-        <x:v>36</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D14" s="19" t="s">
-        <x:v>31</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E14" s="20" t="s">
-        <x:v>30</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F14" s="29" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:6">
@@ -2955,10 +2816,10 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="22" t="s">
-        <x:v>37</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B1" s="23" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
@@ -2971,18 +2832,18 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="24" t="s">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B3" s="26" t="s">
-        <x:v>13</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="24" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B4" s="26" t="s">
-        <x:v>24</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
@@ -2990,31 +2851,31 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B5" s="26" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="24" t="s">
-        <x:v>41</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B6" s="26" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="24" t="s">
-        <x:v>38</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B7" s="26" t="s">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="25" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B8" s="27" t="s">
-        <x:v>4</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/공지사항.xlsx
+++ b/공지사항.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="25340" windowHeight="11490" tabRatio="500"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="4294939900" windowHeight="17090" tabRatio="500"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="공지사항" sheetId="1" r:id="rId4"/>
@@ -20,132 +20,150 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="42">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="48">
+  <x:si>
+    <x:t>지역 어르신들을 위한 봉사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세계선교주일 (10월 첫째 주일)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세계선교주일 헌금을 기도로 준비하시기 바랍니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영문 오픈하우스 (8/22, 토)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영문출발은 오전10시 30분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수원역 무료급식(7월14일)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Y=중요공지, N=일반공지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시작일·종료일 사이에만 앱에 표시됩니다. 중요=Y인 공지는 상단에 강조됩니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>작성 방법</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여성캠프 안내</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소그룹 모임을 매월 첫째주와 셋째주로 변경 합니다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장소 :  구세군사관대학원대학교, 8/15일(토)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장소 : 과천영문 (세부일정 추후 공지예정)</x:t>
+  </x:si>
   <x:si>
     <x:t>공지 노출 시작일. yyyy-mm-dd 형식</x:t>
   </x:si>
   <x:si>
-    <x:t>소그룹 모임을 매월 첫째주와 셋째주로 변경 합니다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장소 :  구세군사관대학원대학교, 8/15일(토)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장소 : 과천영문 (세부일정 추후 공지예정)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시작일·종료일 사이에만 앱에 표시됩니다. 중요=Y인 공지는 상단에 강조됩니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영문출발은 오전10시 30분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Y=중요공지, N=일반공지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수원역 무료급식(7월14일)</x:t>
+    <x:t>영문 악대캠프 시행</x:t>
+  </x:si>
+  <x:si>
+    <x:t>박옥영사관님 추도예배</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소그룹 모임 변경안내</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공지사항 표준양식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바자회 물품 후원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>짧고 분명하게 작성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공지/안내/행사/예배/교육/전도/봉사/회의/기타 중 선택</x:t>
+  </x:si>
+  <x:si>
+    <x:t>salvation land 어린이 캠프(7월25일)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장소 : 세종하늘공원, 8/8(토), 오전9시 영문출발</x:t>
+  </x:si>
+  <x:si>
+    <x:t>중요</x:t>
+  </x:si>
+  <x:si>
+    <x:t>항목</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종료일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주의</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시작일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>행사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>봉사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>제목</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Y</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일정·장소·준비사항 등을 자세히 작성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가정단에서 바자회 물품 후원을 받습니다</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">담임사관님, 목양담당사관님 여름휴가 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>휴가기간 : 8/3(월)~8/8(토)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공지 노출 종료일. 해당 날짜까지 표시</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장소 : 과천영문, 8/13일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>열 이름과 순서를 변경하지 마세요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>남서울지방 여름성회(8/12~14)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구세군사관대학원대학교에서 진행</x:t>
   </x:si>
   <x:si>
     <x:t>청년부 점심식사 매식(8/16)</x:t>
   </x:si>
   <x:si>
-    <x:t>공지사항 표준양식</x:t>
-  </x:si>
-  <x:si>
-    <x:t>바자회 물품 후원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>짧고 분명하게 작성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영문 악대캠프 시행</x:t>
-  </x:si>
-  <x:si>
-    <x:t>박옥영사관님 추도예배</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소그룹 모임 변경안내</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공지/안내/행사/예배/교육/전도/봉사/회의/기타 중 선택</x:t>
-  </x:si>
-  <x:si>
-    <x:t>salvation land 어린이 캠프(7월25일)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장소 : 세종하늘공원, 8/8(토), 오전9시 영문출발</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여성캠프 안내</x:t>
-  </x:si>
-  <x:si>
-    <x:t>작성 방법</x:t>
-  </x:si>
-  <x:si>
-    <x:t>휴가기간 : 8/3(월)~8/8(토)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가정단에서 바자회 물품 후원을 받습니다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공지 노출 종료일. 해당 날짜까지 표시</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">담임사관님, 목양담당사관님 여름휴가 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>일정·장소·준비사항 등을 자세히 작성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종료일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>항목</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주의</x:t>
-  </x:si>
-  <x:si>
-    <x:t>중요</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Y</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시작일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>제목</x:t>
-  </x:si>
-  <x:si>
-    <x:t>행사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>봉사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장소 : 과천영문, 8/13일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>남서울지방 여름성회(8/12~14)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구세군사관대학원대학교에서 진행</x:t>
-  </x:si>
-  <x:si>
-    <x:t>열 이름과 순서를 변경하지 마세요.</x:t>
-  </x:si>
-  <x:si>
     <x:t>여름 수련회 비용마련을 위한 매식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>남서울지방 주관, 영문 돕는손 모금 부문 우수상 수상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여성캠프, 가정단 돕는손 부문 우수상 수상</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -807,6 +825,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ff8e1b33"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1021,7 +1040,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:6" ht="32" customHeight="1">
       <x:c r="A1" s="30" t="s">
-        <x:v>9</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B1" s="30"/>
       <x:c r="C1" s="30"/>
@@ -1031,7 +1050,7 @@
     </x:row>
     <x:row r="2" spans="1:6" ht="28" customHeight="1">
       <x:c r="A2" s="31" t="s">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B2" s="31"/>
       <x:c r="C2" s="31"/>
@@ -1041,22 +1060,22 @@
     </x:row>
     <x:row r="4" spans="1:6" ht="24" customHeight="1">
       <x:c r="A4" s="2" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B4" s="3" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C4" s="3" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B4" s="3" t="s">
+      <x:c r="D4" s="3" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E4" s="3" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C4" s="3" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D4" s="3" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E4" s="3" t="s">
-        <x:v>36</x:v>
-      </x:c>
       <x:c r="F4" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:6">
@@ -1067,16 +1086,16 @@
         <x:v>46217</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D5" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E5" s="14" t="s">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F5" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6">
@@ -1087,16 +1106,16 @@
         <x:v>46234</x:v>
       </x:c>
       <x:c r="C6" s="8" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D6" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E6" s="15" t="s">
-        <x:v>21</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F6" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:6">
@@ -1107,16 +1126,16 @@
         <x:v>46222</x:v>
       </x:c>
       <x:c r="C7" s="5" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D7" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E7" s="14" t="s">
-        <x:v>1</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F7" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6">
@@ -1127,16 +1146,16 @@
         <x:v>46228</x:v>
       </x:c>
       <x:c r="C8" s="19" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D8" s="19" t="s">
-        <x:v>16</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E8" s="20" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F8" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:6">
@@ -1147,16 +1166,16 @@
         <x:v>46249</x:v>
       </x:c>
       <x:c r="C9" s="19" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D9" s="19" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E9" s="20" t="s">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F9" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:6">
@@ -1167,16 +1186,16 @@
         <x:v>46242</x:v>
       </x:c>
       <x:c r="C10" s="19" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D10" s="19" t="s">
-        <x:v>23</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E10" s="20" t="s">
-        <x:v>20</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F10" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:6">
@@ -1187,16 +1206,16 @@
         <x:v>46249</x:v>
       </x:c>
       <x:c r="C11" s="19" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D11" s="19" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E11" s="20" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F11" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:6">
@@ -1207,16 +1226,16 @@
         <x:v>46249</x:v>
       </x:c>
       <x:c r="C12" s="19" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D12" s="19" t="s">
-        <x:v>18</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E12" s="20" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F12" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:6">
@@ -1227,16 +1246,16 @@
         <x:v>46249</x:v>
       </x:c>
       <x:c r="C13" s="19" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D13" s="19" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E13" s="20" t="s">
-        <x:v>2</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F13" s="29" t="s">
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:6">
@@ -1247,41 +1266,77 @@
         <x:v>46251</x:v>
       </x:c>
       <x:c r="C14" s="19" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D14" s="19" t="s">
-        <x:v>8</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E14" s="20" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F14" s="29" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:6">
-      <x:c r="A15" s="17"/>
-      <x:c r="B15" s="18"/>
-      <x:c r="C15" s="19"/>
-      <x:c r="D15" s="19"/>
-      <x:c r="E15" s="20"/>
-      <x:c r="F15" s="21"/>
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:6" customFormat="1">
+      <x:c r="A15" s="28">
+        <x:v>46254</x:v>
+      </x:c>
+      <x:c r="B15" s="17">
+        <x:v>46259</x:v>
+      </x:c>
+      <x:c r="C15" s="19" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D15" s="19" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E15" s="20" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F15" s="29" t="s">
+        <x:v>33</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" spans="1:6">
-      <x:c r="A16" s="17"/>
-      <x:c r="B16" s="18"/>
-      <x:c r="C16" s="19"/>
-      <x:c r="D16" s="19"/>
-      <x:c r="E16" s="20"/>
-      <x:c r="F16" s="21"/>
-    </x:row>
-    <x:row r="17" spans="1:6">
-      <x:c r="A17" s="17"/>
-      <x:c r="B17" s="18"/>
-      <x:c r="C17" s="19"/>
-      <x:c r="D17" s="19"/>
-      <x:c r="E17" s="20"/>
-      <x:c r="F17" s="21"/>
+      <x:c r="A16" s="28">
+        <x:v>46254</x:v>
+      </x:c>
+      <x:c r="B16" s="17">
+        <x:v>46315</x:v>
+      </x:c>
+      <x:c r="C16" s="19" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D16" s="19" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E16" s="20" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F16" s="29" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:6" customFormat="1">
+      <x:c r="A17" s="28">
+        <x:v>46254</x:v>
+      </x:c>
+      <x:c r="B17" s="17">
+        <x:v>46264</x:v>
+      </x:c>
+      <x:c r="C17" s="19" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D17" s="19" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E17" s="20" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F17" s="29" t="s">
+        <x:v>33</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" spans="1:6">
       <x:c r="A18" s="17"/>
@@ -2736,59 +2791,74 @@
     <x:mergeCell ref="A1:F1"/>
     <x:mergeCell ref="A2:F2"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="A5:F10 D11:E12 D13:D13 A15:F198">
-    <x:cfRule type="expression" dxfId="12" priority="12">
+  <x:conditionalFormatting sqref="A5:F10 D11:E12 D13:D13 A18:F198">
+    <x:cfRule type="expression" dxfId="12" priority="15">
       <x:formula>$F5="Y"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="A11:A11 C11:C11">
-    <x:cfRule type="expression" dxfId="12" priority="11">
+    <x:cfRule type="expression" dxfId="12" priority="14">
       <x:formula>$F11="Y"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="F11:F11">
-    <x:cfRule type="expression" dxfId="12" priority="10">
+    <x:cfRule type="expression" dxfId="12" priority="13">
       <x:formula>$F11="Y"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="A12:A12 C12:C12">
-    <x:cfRule type="expression" dxfId="12" priority="9">
+    <x:cfRule type="expression" dxfId="12" priority="12">
       <x:formula>$F12="Y"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="F12:F12">
-    <x:cfRule type="expression" dxfId="12" priority="8">
+    <x:cfRule type="expression" dxfId="12" priority="11">
       <x:formula>$F12="Y"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="E13:E13">
+    <x:cfRule type="expression" dxfId="12" priority="10">
+      <x:formula>$F13="Y"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="F13:F13">
+    <x:cfRule type="expression" dxfId="12" priority="9">
+      <x:formula>$F13="Y"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="A13:C13">
     <x:cfRule type="expression" dxfId="12" priority="7">
       <x:formula>$F13="Y"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="F13:F13">
+  <x:conditionalFormatting sqref="B12:B12">
     <x:cfRule type="expression" dxfId="12" priority="6">
-      <x:formula>$F13="Y"</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="A13:C13">
-    <x:cfRule type="expression" dxfId="12" priority="4">
-      <x:formula>$F13="Y"</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="B12:B12">
-    <x:cfRule type="expression" dxfId="12" priority="3">
       <x:formula>$F12="Y"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="B11:B11">
-    <x:cfRule type="expression" dxfId="12" priority="2">
+    <x:cfRule type="expression" dxfId="12" priority="5">
       <x:formula>$F11="Y"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="A14:F14">
+    <x:cfRule type="expression" dxfId="12" priority="4">
+      <x:formula>$F14="Y"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="A15:F15">
+    <x:cfRule type="expression" dxfId="12" priority="3">
+      <x:formula>$F15="Y"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="A16:F16">
+    <x:cfRule type="expression" dxfId="12" priority="2">
+      <x:formula>$F16="Y"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="A17:F17">
     <x:cfRule type="expression" dxfId="12" priority="1">
-      <x:formula>$F14="Y"</x:formula>
+      <x:formula>$F17="Y"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="2">
@@ -2816,55 +2886,55 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="22" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B1" s="23" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="24" t="s">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B2" s="26" t="s">
-        <x:v>0</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="24" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B3" s="26" t="s">
-        <x:v>22</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="24" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B4" s="26" t="s">
-        <x:v>15</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="24" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B5" s="26" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="24" t="s">
-        <x:v>36</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B6" s="26" t="s">
-        <x:v>24</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="24" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B7" s="26" t="s">
         <x:v>6</x:v>
@@ -2875,7 +2945,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B8" s="27" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/공지사항.xlsx
+++ b/공지사항.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="4294939900" windowHeight="17090" tabRatio="500"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="25340" windowHeight="11490" tabRatio="500"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="공지사항" sheetId="1" r:id="rId4"/>
@@ -20,7 +20,85 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="48">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="52">
+  <x:si>
+    <x:t>장소 :  구세군사관대학원대학교, 8/15일(토)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공지 노출 시작일. yyyy-mm-dd 형식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장소 : 과천영문 (세부일정 추후 공지예정)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공지 노출 종료일. 해당 날짜까지 표시</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">담임사관님, 목양담당사관님 여름휴가 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>여성캠프, 가정단 돕는손 부문 우수상 수상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>휴가기간 : 8/3(월)~8/8(토)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가정단에서 바자회 물품 후원을 받습니다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일정·장소·준비사항 등을 자세히 작성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전교인 대상으로 야유회 진행, 장소 미정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영문 오픈하우스 (8/22, 토)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세계선교주일 (10월 첫째 주일)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>청년부 점심식사 매식(8/16)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장소 : 과천영문, 8/13일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여름 수련회 비용마련을 위한 매식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>열 이름과 순서를 변경하지 마세요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구세군사관대학원대학교에서 진행</x:t>
+  </x:si>
+  <x:si>
+    <x:t>남서울지방 여름성회(8/12~14)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영문출발은 오전10시 30분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Y=중요공지, N=일반공지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수원역 무료급식(7월14일)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지역 어르신들을 위한 봉사</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">가정단에서 바자회를 진행 합니다. </x:t>
+  </x:si>
+  <x:si>
+    <x:t>시작일·종료일 사이에만 앱에 표시됩니다. 중요=Y인 공지는 상단에 강조됩니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>작성 방법</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여성캠프 안내</x:t>
+  </x:si>
   <x:si>
     <x:t>세계선교주일 헌금을 기도로 준비하시기 바랍니다.</x:t>
   </x:si>
@@ -28,21 +106,15 @@
     <x:t>소그룹 모임을 매월 첫째주와 셋째주로 변경 합니다</x:t>
   </x:si>
   <x:si>
-    <x:t>장소 :  구세군사관대학원대학교, 8/15일(토)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공지 노출 시작일. yyyy-mm-dd 형식</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장소 : 과천영문 (세부일정 추후 공지예정)</x:t>
+    <x:t>바자회 물품 후원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>박옥영사관님 추도예배</x:t>
   </x:si>
   <x:si>
     <x:t>영문 악대캠프 시행</x:t>
   </x:si>
   <x:si>
-    <x:t>박옥영사관님 추도예배</x:t>
-  </x:si>
-  <x:si>
     <x:t>소그룹 모임 변경안내</x:t>
   </x:si>
   <x:si>
@@ -52,82 +124,40 @@
     <x:t>짧고 분명하게 작성</x:t>
   </x:si>
   <x:si>
-    <x:t>바자회 물품 후원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시작일·종료일 사이에만 앱에 표시됩니다. 중요=Y인 공지는 상단에 강조됩니다.</x:t>
+    <x:t>장소 : 세종하늘공원, 8/8(토), 오전9시 영문출발</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공지/안내/행사/예배/교육/전도/봉사/회의/기타 중 선택</x:t>
   </x:si>
   <x:si>
     <x:t>salvation land 어린이 캠프(7월25일)</x:t>
   </x:si>
   <x:si>
-    <x:t>장소 : 세종하늘공원, 8/8(토), 오전9시 영문출발</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공지/안내/행사/예배/교육/전도/봉사/회의/기타 중 선택</x:t>
-  </x:si>
-  <x:si>
     <x:t>남서울지방 주관, 영문 돕는손 모금 부문 우수상 수상</x:t>
   </x:si>
   <x:si>
-    <x:t>작성 방법</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여성캠프 안내</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영문출발은 오전10시 30분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Y=중요공지, N=일반공지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수원역 무료급식(7월14일)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지역 어르신들을 위한 봉사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>청년부 점심식사 매식(8/16)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>세계선교주일 (10월 첫째 주일)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영문 오픈하우스 (8/22, 토)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장소 : 과천영문, 8/13일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여름 수련회 비용마련을 위한 매식</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구세군사관대학원대학교에서 진행</x:t>
-  </x:si>
-  <x:si>
-    <x:t>남서울지방 여름성회(8/12~14)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>열 이름과 순서를 변경하지 마세요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공지 노출 종료일. 해당 날짜까지 표시</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일정·장소·준비사항 등을 자세히 작성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>휴가기간 : 8/3(월)~8/8(토)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가정단에서 바자회 물품 후원을 받습니다</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">담임사관님, 목양담당사관님 여름휴가 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>여성캠프, 가정단 돕는손 부문 우수상 수상</x:t>
+    <x:t>중요</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주의</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>항목</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Y</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>행사</x:t>
   </x:si>
   <x:si>
     <x:t>종료일</x:t>
@@ -136,34 +166,16 @@
     <x:t>제목</x:t>
   </x:si>
   <x:si>
-    <x:t>행사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Y</x:t>
-  </x:si>
-  <x:si>
-    <x:t>항목</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>중요</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주의</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공지</x:t>
+    <x:t>시작일</x:t>
   </x:si>
   <x:si>
     <x:t>봉사</x:t>
   </x:si>
   <x:si>
-    <x:t>시작일</x:t>
+    <x:t>전교인 야유회</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가정단 바자회</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -828,6 +840,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ff8e1b33"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1042,7 +1055,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:6" ht="32" customHeight="1">
       <x:c r="A1" s="31" t="s">
-        <x:v>8</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B1" s="31"/>
       <x:c r="C1" s="31"/>
@@ -1052,7 +1065,7 @@
     </x:row>
     <x:row r="2" spans="1:6" ht="28" customHeight="1">
       <x:c r="A2" s="32" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B2" s="32"/>
       <x:c r="C2" s="32"/>
@@ -1062,22 +1075,22 @@
     </x:row>
     <x:row r="4" spans="1:6" ht="24" customHeight="1">
       <x:c r="A4" s="3" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B4" s="4" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C4" s="4" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D4" s="4" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="B4" s="4" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C4" s="4" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D4" s="4" t="s">
-        <x:v>37</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="F4" s="5" t="s">
-        <x:v>43</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:6">
@@ -1088,7 +1101,7 @@
         <x:v>46217</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D5" s="6" t="s">
         <x:v>20</x:v>
@@ -1097,7 +1110,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F5" s="30" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6">
@@ -1108,16 +1121,16 @@
         <x:v>46234</x:v>
       </x:c>
       <x:c r="C6" s="9" t="s">
-        <x:v>38</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D6" s="9" t="s">
-        <x:v>10</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E6" s="16" t="s">
-        <x:v>33</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F6" s="30" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:6">
@@ -1128,16 +1141,16 @@
         <x:v>46222</x:v>
       </x:c>
       <x:c r="C7" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D7" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E7" s="15" t="s">
-        <x:v>1</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F7" s="30" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6">
@@ -1148,16 +1161,16 @@
         <x:v>46228</x:v>
       </x:c>
       <x:c r="C8" s="20" t="s">
-        <x:v>38</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D8" s="20" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E8" s="21" t="s">
-        <x:v>27</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F8" s="30" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:6">
@@ -1168,16 +1181,16 @@
         <x:v>46249</x:v>
       </x:c>
       <x:c r="C9" s="20" t="s">
-        <x:v>38</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D9" s="20" t="s">
-        <x:v>28</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E9" s="21" t="s">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F9" s="30" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:6">
@@ -1188,16 +1201,16 @@
         <x:v>46242</x:v>
       </x:c>
       <x:c r="C10" s="20" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D10" s="20" t="s">
-        <x:v>34</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E10" s="21" t="s">
-        <x:v>32</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F10" s="30" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:6">
@@ -1208,16 +1221,16 @@
         <x:v>46249</x:v>
       </x:c>
       <x:c r="C11" s="20" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D11" s="20" t="s">
-        <x:v>6</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E11" s="21" t="s">
-        <x:v>13</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F11" s="30" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:6">
@@ -1228,16 +1241,16 @@
         <x:v>46254</x:v>
       </x:c>
       <x:c r="C12" s="20" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D12" s="20" t="s">
-        <x:v>17</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E12" s="21" t="s">
-        <x:v>25</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F12" s="30" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:6">
@@ -1248,16 +1261,16 @@
         <x:v>46254</x:v>
       </x:c>
       <x:c r="C13" s="20" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D13" s="20" t="s">
-        <x:v>5</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E13" s="21" t="s">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F13" s="30" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:6">
@@ -1268,16 +1281,16 @@
         <x:v>46254</x:v>
       </x:c>
       <x:c r="C14" s="20" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D14" s="20" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E14" s="21" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F14" s="30" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:6" s="1" customFormat="1">
@@ -1288,16 +1301,16 @@
         <x:v>46259</x:v>
       </x:c>
       <x:c r="C15" s="20" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D15" s="20" t="s">
-        <x:v>24</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E15" s="21" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="F15" s="30" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:6">
@@ -1308,16 +1321,16 @@
         <x:v>46315</x:v>
       </x:c>
       <x:c r="C16" s="20" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D16" s="20" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E16" s="21" t="s">
-        <x:v>0</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F16" s="30" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:6" s="1" customFormat="1">
@@ -1328,41 +1341,65 @@
         <x:v>46264</x:v>
       </x:c>
       <x:c r="C17" s="20" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D17" s="20" t="s">
-        <x:v>35</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E17" s="21" t="s">
-        <x:v>15</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F17" s="30" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:6">
-      <x:c r="A18" s="18"/>
-      <x:c r="B18" s="19"/>
-      <x:c r="C18" s="20"/>
-      <x:c r="D18" s="20"/>
-      <x:c r="E18" s="21"/>
-      <x:c r="F18" s="22"/>
-    </x:row>
-    <x:row r="19" spans="1:6">
-      <x:c r="A19" s="18"/>
-      <x:c r="B19" s="19"/>
-      <x:c r="C19" s="20"/>
-      <x:c r="D19" s="20"/>
-      <x:c r="E19" s="21"/>
-      <x:c r="F19" s="22"/>
-    </x:row>
-    <x:row r="20" spans="1:6">
-      <x:c r="A20" s="18"/>
-      <x:c r="B20" s="19"/>
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:6" customFormat="1">
+      <x:c r="A18" s="29">
+        <x:v>46270</x:v>
+      </x:c>
+      <x:c r="B18" s="18">
+        <x:v>46295</x:v>
+      </x:c>
+      <x:c r="C18" s="20" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D18" s="20" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E18" s="21" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F18" s="30" t="s">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:6" customFormat="1">
+      <x:c r="A19" s="29">
+        <x:v>46270</x:v>
+      </x:c>
+      <x:c r="B19" s="18">
+        <x:v>46315</x:v>
+      </x:c>
+      <x:c r="C19" s="20" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D19" s="20" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E19" s="21" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F19" s="30" t="s">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:6" customFormat="1">
+      <x:c r="A20" s="29"/>
+      <x:c r="B20" s="18"/>
       <x:c r="C20" s="20"/>
       <x:c r="D20" s="20"/>
       <x:c r="E20" s="21"/>
-      <x:c r="F20" s="22"/>
+      <x:c r="F20" s="30"/>
     </x:row>
     <x:row r="21" spans="1:6">
       <x:c r="A21" s="18"/>
@@ -2793,84 +2830,99 @@
     <x:mergeCell ref="A1:F1"/>
     <x:mergeCell ref="A2:F2"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="A5:F10 D11:E12 D13:D13 A18:F198">
-    <x:cfRule type="expression" dxfId="12" priority="17">
+  <x:conditionalFormatting sqref="A5:F10 D11:E12 D13:D13 A21:F198">
+    <x:cfRule type="expression" dxfId="12" priority="20">
       <x:formula>$F5="Y"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="A11:A11 C11:C11">
-    <x:cfRule type="expression" dxfId="12" priority="16">
+    <x:cfRule type="expression" dxfId="12" priority="19">
       <x:formula>$F11="Y"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="F11:F11">
-    <x:cfRule type="expression" dxfId="12" priority="15">
+    <x:cfRule type="expression" dxfId="12" priority="18">
       <x:formula>$F11="Y"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="A12:A12 C12:C12">
-    <x:cfRule type="expression" dxfId="12" priority="14">
+    <x:cfRule type="expression" dxfId="12" priority="17">
       <x:formula>$F12="Y"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="F12:F12">
-    <x:cfRule type="expression" dxfId="12" priority="13">
+    <x:cfRule type="expression" dxfId="12" priority="16">
       <x:formula>$F12="Y"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="E13:E13">
+    <x:cfRule type="expression" dxfId="12" priority="15">
+      <x:formula>$F13="Y"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="F13:F13">
+    <x:cfRule type="expression" dxfId="12" priority="14">
+      <x:formula>$F13="Y"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="A13:A13 C13:C13">
     <x:cfRule type="expression" dxfId="12" priority="12">
       <x:formula>$F13="Y"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="F13:F13">
+  <x:conditionalFormatting sqref="B12:B12">
     <x:cfRule type="expression" dxfId="12" priority="11">
-      <x:formula>$F13="Y"</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="A13:A13 C13:C13">
-    <x:cfRule type="expression" dxfId="12" priority="9">
-      <x:formula>$F13="Y"</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="B12:B12">
-    <x:cfRule type="expression" dxfId="12" priority="8">
       <x:formula>$F12="Y"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="B11:B11">
-    <x:cfRule type="expression" dxfId="12" priority="7">
+    <x:cfRule type="expression" dxfId="12" priority="10">
       <x:formula>$F11="Y"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="A14:A14 C14:F14">
-    <x:cfRule type="expression" dxfId="12" priority="6">
+    <x:cfRule type="expression" dxfId="12" priority="9">
       <x:formula>$F14="Y"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="A15:F15">
-    <x:cfRule type="expression" dxfId="12" priority="5">
+    <x:cfRule type="expression" dxfId="12" priority="8">
       <x:formula>$F15="Y"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="A16:F16">
-    <x:cfRule type="expression" dxfId="12" priority="4">
+    <x:cfRule type="expression" dxfId="12" priority="7">
       <x:formula>$F16="Y"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="A17:F17">
-    <x:cfRule type="expression" dxfId="12" priority="3">
+    <x:cfRule type="expression" dxfId="12" priority="6">
       <x:formula>$F17="Y"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="B13:B13">
-    <x:cfRule type="expression" dxfId="12" priority="2">
+    <x:cfRule type="expression" dxfId="12" priority="5">
       <x:formula>$F13="Y"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="B14:B14">
+    <x:cfRule type="expression" dxfId="12" priority="4">
+      <x:formula>$F14="Y"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="A18:F18">
+    <x:cfRule type="expression" dxfId="12" priority="3">
+      <x:formula>$F18="Y"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="A19:F19">
+    <x:cfRule type="expression" dxfId="12" priority="2">
+      <x:formula>$F19="Y"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="A20:F20">
     <x:cfRule type="expression" dxfId="12" priority="1">
-      <x:formula>$F14="Y"</x:formula>
+      <x:formula>$F20="Y"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="2">
@@ -2898,42 +2950,42 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="23" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B1" s="24" t="s">
-        <x:v>16</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="25" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B2" s="27" t="s">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="25" t="s">
-        <x:v>36</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B3" s="27" t="s">
-        <x:v>30</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="25" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B4" s="27" t="s">
-        <x:v>14</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="25" t="s">
-        <x:v>37</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B5" s="27" t="s">
-        <x:v>9</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
@@ -2941,12 +2993,12 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B6" s="27" t="s">
-        <x:v>31</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="25" t="s">
-        <x:v>43</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B7" s="27" t="s">
         <x:v>19</x:v>
@@ -2954,10 +3006,10 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="26" t="s">
-        <x:v>44</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B8" s="28" t="s">
-        <x:v>29</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
